--- a/RecepcionMercaderia/planilla_de_apoyo_del_prototipo.xlsx
+++ b/RecepcionMercaderia/planilla_de_apoyo_del_prototipo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cande\source\repos\GrupoC\RecepcionMercaderia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A79C485-7035-4D28-8056-497E6B4F42CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DAD11DF-4A04-4465-AFEA-8F61034BE6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Si</t>
   </si>
   <si>
-    <t>Clientes con contrato vigente: Distribuidora Andina, ElectroSur, Ferretería Industrial Norte, Textil Pampa</t>
-  </si>
-  <si>
     <t>Solo letras y espacios. Debe coincidir con un cliente de la lista (sin distinguir mayúsculas). Si se cambia con ítems cargados, se pide confirmación y se quitan los ítems del detalle.</t>
   </si>
   <si>
@@ -124,15 +121,6 @@
   </si>
   <si>
     <t>Solo números; el guion se agrega solo después del 5° número. Debe tener los 13 números. No puede estar ya registrado para el cliente elegido.</t>
-  </si>
-  <si>
-    <t>"N° Remito: solo números. El guion se agrega solo después del 5° número."
-"El N° de remito lleva 13 números: faltan [n]."
-"El remito N° [nro] ya fue registrado para el cliente [cliente]. Verifique el número en el remito que entrega el transportista."
-Al confirmar: "El N° de remito debe tener 13 números: 5 del punto de venta, un guion y 8 del comprobante. Ejemplo: 00001-00012345."</t>
-  </si>
-  <si>
-    <t>Remitos ya registrados (datos de prueba): Distribuidora Andina 00001-00004521 y 00001-00004522; ElectroSur 00003-00001187; Textil Pampa 00002-00000915; Ferretería Industrial Norte 00005-00010233. Si el remito está repetido se borra el campo y queda marcado en rojo.</t>
   </si>
   <si>
     <t>Transportista</t>
@@ -334,6 +322,15 @@
   </si>
   <si>
     <t xml:space="preserve">SKU dados de alta para el cliente elegido. </t>
+  </si>
+  <si>
+    <t>Remitos ya registrados</t>
+  </si>
+  <si>
+    <t>Clientes con contrato vigente</t>
+  </si>
+  <si>
+    <t>"N° Remito: solo números. El guion se agrega solo después del 5° número.""El N° de remito lleva 13 números: faltan [n].""El remito N° [nro] ya fue registrado para el cliente [cliente]. Verifique el número en el remito que entrega el transportista."Al confirmar: "El N° de remito debe tener 13 números: 5 del punto de venta, un guion y 8 del comprobante. Ejemplo: 00001-00012345."</t>
   </si>
 </sst>
 </file>
@@ -830,7 +827,8 @@
     <col min="5" max="5" width="20.5546875" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
     <col min="10" max="10" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -928,7 +926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -948,59 +946,59 @@
         <v>26</v>
       </c>
       <c r="G5" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>28</v>
-      </c>
       <c r="I5" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="352.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="H6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>33</v>
-      </c>
       <c r="I6" s="14" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" s="13">
         <v>60</v>
@@ -1012,27 +1010,27 @@
         <v>26</v>
       </c>
       <c r="G7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:10" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="13">
         <v>10</v>
@@ -1044,27 +1042,27 @@
         <v>26</v>
       </c>
       <c r="G8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:10" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" s="13">
         <v>60</v>
@@ -1076,27 +1074,27 @@
         <v>26</v>
       </c>
       <c r="G9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:10" ht="179.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D10" s="13">
         <v>7</v>
@@ -1108,27 +1106,27 @@
         <v>26</v>
       </c>
       <c r="G10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D11" s="13">
         <v>20</v>
@@ -1137,28 +1135,28 @@
         <v>26</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" s="13">
         <v>6</v>
@@ -1167,30 +1165,30 @@
         <v>26</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" s="13">
         <v>6</v>
@@ -1199,30 +1197,30 @@
         <v>26</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:10" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>25</v>
@@ -1234,19 +1232,19 @@
         <v>26</v>
       </c>
       <c r="G14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10" ht="122.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>11</v>
       </c>
@@ -1254,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D15" s="13">
         <v>200</v>
@@ -1263,10 +1261,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>25</v>
@@ -1275,18 +1273,18 @@
         <v>25</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>25</v>
@@ -1298,16 +1296,16 @@
         <v>26</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="66" x14ac:dyDescent="0.3">
@@ -1315,10 +1313,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>25</v>
@@ -1330,16 +1328,16 @@
         <v>26</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
